--- a/Teensy_2026_Commands.xlsx
+++ b/Teensy_2026_Commands.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29711"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/37285d1b3bdcff71/Desktop/AG/Teensy_Code_2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="360" documentId="8_{D37A0355-1AB5-48C8-9ECF-435C4D722AD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2BF16B19-B75F-4BF2-9D29-B9C291C38FFC}"/>
+  <xr:revisionPtr revIDLastSave="365" documentId="8_{D37A0355-1AB5-48C8-9ECF-435C4D722AD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6750F184-EE4B-491C-8179-0E09443EDAF1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -71,22 +71,37 @@
     <t>Drive</t>
   </si>
   <si>
+    <t>Fahren in bestimmte Richtung (Dir) mit drehung um eigene Achse (Angle) und Geschwindigkeit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Dir": Fahrtrichtung  (-180° bis 180°)  / "Angle": Blickrichtung (-180° bis 180)  /  "Speed" : 0 bis 100 </t>
+  </si>
+  <si>
     <t>Stop</t>
   </si>
   <si>
     <t>Roboter Komplett Anhalten ( Motor Stop )</t>
   </si>
   <si>
+    <t>Break</t>
+  </si>
+  <si>
+    <t>Roboter Komplett Bremsen ( Motor Break )</t>
+  </si>
+  <si>
     <t>Robot.Kicker</t>
   </si>
   <si>
+    <t>On</t>
+  </si>
+  <si>
     <t>-</t>
   </si>
   <si>
-    <t>On</t>
-  </si>
-  <si>
     <t>Off</t>
+  </si>
+  <si>
+    <t>System</t>
   </si>
   <si>
     <t>Button_Update</t>
@@ -256,9 +271,6 @@
     <t>Motor AUS</t>
   </si>
   <si>
-    <t>Break</t>
-  </si>
-  <si>
     <t>Motor aktiv Bremsen</t>
   </si>
   <si>
@@ -358,6 +370,63 @@
     <t>US</t>
   </si>
   <si>
+    <t>Line</t>
+  </si>
+  <si>
+    <t>Liest alle ineren Line Sensoren aus und Speichert diese (1)</t>
+  </si>
+  <si>
+    <t>read_VW</t>
+  </si>
+  <si>
+    <t>Liest 8 äußere Line Sensoren aus und Speichert diese (1)</t>
+  </si>
+  <si>
+    <t>Cam</t>
+  </si>
+  <si>
+    <t>Setup der Camera (2)</t>
+  </si>
+  <si>
+    <t>Update der Camera (1)</t>
+  </si>
+  <si>
+    <t>Mouse</t>
+  </si>
+  <si>
+    <t>Setup des Moussensors (2)</t>
+  </si>
+  <si>
+    <t>Update des Moussensors (1)</t>
+  </si>
+  <si>
+    <t>giveSpeed</t>
+  </si>
+  <si>
+    <t>Ausgeben des allgemeinen bewegungs Speed</t>
+  </si>
+  <si>
+    <t>BallCalc</t>
+  </si>
+  <si>
+    <t>getAngle</t>
+  </si>
+  <si>
+    <t>Ballanfahrts Berechnung</t>
+  </si>
+  <si>
+    <t>"inAngle": Ballwinkel , "dist":  Balldistance</t>
+  </si>
+  <si>
+    <t>LineCalc</t>
+  </si>
+  <si>
+    <t>Calc</t>
+  </si>
+  <si>
+    <t>Linien Berechnung</t>
+  </si>
+  <si>
     <t>( 1 ) Fußnote :</t>
   </si>
   <si>
@@ -370,15 +439,336 @@
     <t>( sollte einmal am beginn des Programms aufgerufen werden )</t>
   </si>
   <si>
+    <t xml:space="preserve">( Diese Werte werden nicht im Programm verändert nur gelesen. Es sind Variablen auf die von überall zugegriffen werden kann. Sie können im Ordner Elementar unter Param oder enum verändert oder erweitert werden </t>
+  </si>
+  <si>
     <t>Parameter ( Einstellungen ) in Elementar Ordner</t>
   </si>
   <si>
+    <t>Es wird kein Prefix so wie der Klassen name oder etwas in der Art verwendet. Einfach den Variablen Namen aufrufen. )</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Speicherort</t>
+  </si>
+  <si>
+    <t>Standartwert</t>
+  </si>
+  <si>
+    <t>Nutzen</t>
+  </si>
+  <si>
+    <t>HighSpeed</t>
+  </si>
+  <si>
+    <t>Param</t>
+  </si>
+  <si>
+    <t>LowSpeed</t>
+  </si>
+  <si>
+    <t>Kp</t>
+  </si>
+  <si>
+    <t>Kd</t>
+  </si>
+  <si>
+    <t>Ki</t>
+  </si>
+  <si>
+    <t>PID_Mult</t>
+  </si>
+  <si>
+    <t>PID einfluss während fahrt bewegung</t>
+  </si>
+  <si>
+    <t>PID_Konstante</t>
+  </si>
+  <si>
+    <t>PID Speed</t>
+  </si>
+  <si>
+    <t>LDR_Schwelle</t>
+  </si>
+  <si>
+    <t>Ab welchem Lichtwert der LDR auslöst</t>
+  </si>
+  <si>
+    <t>Line_Schwelle</t>
+  </si>
+  <si>
+    <t>Ab welchem Lichtwert der LinienSensor auslöst</t>
+  </si>
+  <si>
+    <t>Motor_Frequency</t>
+  </si>
+  <si>
+    <t>Motor PWM Frquenz</t>
+  </si>
+  <si>
+    <t>Interface_Frequency</t>
+  </si>
+  <si>
+    <t>Abfrage Frequenz der Buttons und Schalter ( =&gt; 100millis )</t>
+  </si>
+  <si>
+    <t>US_Frequency</t>
+  </si>
+  <si>
+    <t>Abfrage Frequenz der US Sensoren ( =&gt; 100millis )</t>
+  </si>
+  <si>
+    <t>FocalLenght</t>
+  </si>
+  <si>
+    <t>ImageWidth</t>
+  </si>
+  <si>
+    <t>ImageHeight</t>
+  </si>
+  <si>
+    <t>ObjectSize</t>
+  </si>
+  <si>
+    <t>distFactor</t>
+  </si>
+  <si>
+    <t>Ir_Min[16]</t>
+  </si>
+  <si>
+    <t>0,0,0,0,0,…</t>
+  </si>
+  <si>
+    <t>Kalibrationswerte für ir Sensoren falls es probleme gibt.</t>
+  </si>
+  <si>
+    <t>Ir_Max[16]</t>
+  </si>
+  <si>
+    <t>3000,3000,…</t>
+  </si>
+  <si>
+    <t>VR_Motor</t>
+  </si>
+  <si>
+    <t>enum</t>
+  </si>
+  <si>
+    <t>Motor Port an welchem der Motor VornRechts angeschlossen ist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anmerkung: Diese Bezeichnung wird immer zum aufrufen aller Motor befehle verwendet um schnelle Logik mit bezug zur wirklich keit zu gewährleisten. </t>
+  </si>
+  <si>
+    <t>VL_Motor</t>
+  </si>
+  <si>
+    <t>Motor Port an welchem der Motor VornLinks angeschlossen ist</t>
+  </si>
+  <si>
+    <t>Motor befehl sieht dann so aus : Motor.On(VR_Motor,100);</t>
+  </si>
+  <si>
+    <t>HR_Motor</t>
+  </si>
+  <si>
+    <t>Motor Port an welchem der Motor HintenRechts angeschlossen ist</t>
+  </si>
+  <si>
+    <t>HL_Motor</t>
+  </si>
+  <si>
+    <t>Motor Port an welchem der Motor HintenLinks angeschlossen ist</t>
+  </si>
+  <si>
+    <t>VR_Speed_Port</t>
+  </si>
+  <si>
+    <t>PWM Port</t>
+  </si>
+  <si>
+    <t>VL_Speed_Port</t>
+  </si>
+  <si>
+    <t>HR_Speed_Port</t>
+  </si>
+  <si>
+    <t>HL_Speed_Port</t>
+  </si>
+  <si>
+    <t>VR_ExpanderA</t>
+  </si>
+  <si>
+    <t>Richtungs Port  am Teensy</t>
+  </si>
+  <si>
+    <t>VR_ExpanderB</t>
+  </si>
+  <si>
+    <t>VL_ExpanderA</t>
+  </si>
+  <si>
+    <t>VL_ExpanderB</t>
+  </si>
+  <si>
+    <t>HR_ExpanderA</t>
+  </si>
+  <si>
+    <t>HR_ExpanderB</t>
+  </si>
+  <si>
+    <t>HL_ExpanderA</t>
+  </si>
+  <si>
+    <t>HL_ExpanderB</t>
+  </si>
+  <si>
+    <t>US_Left</t>
+  </si>
+  <si>
+    <t>0x70</t>
+  </si>
+  <si>
+    <t>Addresse</t>
+  </si>
+  <si>
+    <t>US_Right</t>
+  </si>
+  <si>
+    <t>0x71</t>
+  </si>
+  <si>
+    <t>LDR_Port</t>
+  </si>
+  <si>
+    <t>Port am Teensy</t>
+  </si>
+  <si>
+    <t>Start_Port</t>
+  </si>
+  <si>
+    <t>Schuss_Port</t>
+  </si>
+  <si>
+    <t>Kicker_Port</t>
+  </si>
+  <si>
+    <t>Output_Reg</t>
+  </si>
+  <si>
+    <t>0x01</t>
+  </si>
+  <si>
+    <t>register</t>
+  </si>
+  <si>
+    <t>Input_Reg</t>
+  </si>
+  <si>
+    <t>0x00</t>
+  </si>
+  <si>
+    <t>Config_Reg</t>
+  </si>
+  <si>
+    <t>0x03</t>
+  </si>
+  <si>
+    <t>Input_Mode</t>
+  </si>
+  <si>
+    <t>0xFF</t>
+  </si>
+  <si>
+    <t>Output_Mode</t>
+  </si>
+  <si>
+    <t>All_Off</t>
+  </si>
+  <si>
+    <t>All_On</t>
+  </si>
+  <si>
+    <t>I2C_ITF_Main</t>
+  </si>
+  <si>
+    <t>0x20</t>
+  </si>
+  <si>
+    <t>I2C_Motor</t>
+  </si>
+  <si>
+    <t>0x21</t>
+  </si>
+  <si>
+    <t>I2C_ITF_Ex</t>
+  </si>
+  <si>
+    <t>0x22</t>
+  </si>
+  <si>
+    <t>I2C_INA219</t>
+  </si>
+  <si>
+    <t>0x40</t>
+  </si>
+  <si>
+    <t>I2C_BUS</t>
+  </si>
+  <si>
+    <t>Wire1</t>
+  </si>
+  <si>
+    <t>I2C Port auf Basic Platine</t>
+  </si>
+  <si>
+    <t>I2C_SPEED</t>
+  </si>
+  <si>
+    <t>Frequenz ( 1MHz )</t>
+  </si>
+  <si>
+    <t>UART_Debug</t>
+  </si>
+  <si>
+    <t>Serial</t>
+  </si>
+  <si>
+    <t>Serieller Debug Port</t>
+  </si>
+  <si>
+    <t>UART_Pixy</t>
+  </si>
+  <si>
+    <t>Serial3</t>
+  </si>
+  <si>
+    <t>Serieller Cam Port</t>
+  </si>
+  <si>
+    <t>UART_1</t>
+  </si>
+  <si>
+    <t>Serial6</t>
+  </si>
+  <si>
+    <t>Serieller Port 1</t>
+  </si>
+  <si>
+    <t>UART_2</t>
+  </si>
+  <si>
+    <t>Serial7</t>
+  </si>
+  <si>
+    <t>Serieller Port 2</t>
+  </si>
+  <si>
     <t xml:space="preserve">Variablen und Daten </t>
   </si>
   <si>
-    <t>Name</t>
-  </si>
-  <si>
     <t>Typ</t>
   </si>
   <si>
@@ -430,84 +820,36 @@
     <t>Winkel des Balls ( -180 bis 180 )</t>
   </si>
   <si>
-    <t>Line</t>
-  </si>
-  <si>
-    <t>read_VW</t>
-  </si>
-  <si>
-    <t>Liest alle ineren Line Sensoren aus und Speichert diese (1)</t>
-  </si>
-  <si>
-    <t>Liest 8 äußere Line Sensoren aus und Speichert diese (1)</t>
-  </si>
-  <si>
-    <t>Roboter Komplett Bremsen ( Motor Break )</t>
-  </si>
-  <si>
-    <t>Cam</t>
-  </si>
-  <si>
-    <t>Mouse</t>
-  </si>
-  <si>
-    <t>giveSpeed</t>
-  </si>
-  <si>
-    <t>Setup der Camera (2)</t>
-  </si>
-  <si>
-    <t>Update der Camera (1)</t>
-  </si>
-  <si>
-    <t>Setup des Moussensors (2)</t>
-  </si>
-  <si>
-    <t>Update des Moussensors (1)</t>
-  </si>
-  <si>
-    <t>Ausgeben des allgemeinen bewegungs Speed</t>
-  </si>
-  <si>
-    <t>Fahren in bestimmte Richtung (Dir) mit drehung um eigene Achse (Angle) und Geschwindigkeit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"Dir": Fahrtrichtung  (-180° bis 180°)  / "Angle": Blickrichtung (-180° bis 180)  /  "Speed" : 0 bis 100 </t>
-  </si>
-  <si>
     <t>Summe</t>
   </si>
   <si>
     <t>Stärke des ineren Rings</t>
   </si>
   <si>
+    <t>Summe_VW</t>
+  </si>
+  <si>
     <t>Stärke des äußeren Rings</t>
   </si>
   <si>
-    <t>Summe_VW</t>
-  </si>
-  <si>
     <t>Raw</t>
   </si>
   <si>
+    <t>float[32]</t>
+  </si>
+  <si>
+    <t>Liste mit 32 digitalen Werten ob Linie erkannt wurde oder nicht ( 1 oder 0 )</t>
+  </si>
+  <si>
     <t>Raw_VW</t>
   </si>
   <si>
-    <t>float[32]</t>
-  </si>
-  <si>
     <t>float[8]</t>
   </si>
   <si>
-    <t>Liste mit 32 digitalen Werten ob Linie erkannt wurde oder nicht ( 1 oder 0 )</t>
-  </si>
-  <si>
     <t>Liste mit 8 digitalen Werten ob Linie erkannt wurde oder nicht ( 1 oder 0 )</t>
   </si>
   <si>
-    <t>System</t>
-  </si>
-  <si>
     <t>Start</t>
   </si>
   <si>
@@ -517,27 +859,6 @@
     <t xml:space="preserve">Wert ob Start schalter gedrückt oder nicht </t>
   </si>
   <si>
-    <t>BallCalc</t>
-  </si>
-  <si>
-    <t>getAngle</t>
-  </si>
-  <si>
-    <t>Ballanfahrts Berechnung</t>
-  </si>
-  <si>
-    <t>"inAngle": Ballwinkel , "dist":  Balldistance</t>
-  </si>
-  <si>
-    <t>LineCalc</t>
-  </si>
-  <si>
-    <t>Calc</t>
-  </si>
-  <si>
-    <t>Linien Berechnung</t>
-  </si>
-  <si>
     <t>RawAngle</t>
   </si>
   <si>
@@ -563,334 +884,13 @@
   </si>
   <si>
     <t>Ballanfahrtswinkel</t>
-  </si>
-  <si>
-    <t>Es wird kein Prefix so wie der Klassen name oder etwas in der Art verwendet. Einfach den Variablen Namen aufrufen. )</t>
-  </si>
-  <si>
-    <t>HighSpeed</t>
-  </si>
-  <si>
-    <t>Speicherort</t>
-  </si>
-  <si>
-    <t>Standartwert</t>
-  </si>
-  <si>
-    <t>Nutzen</t>
-  </si>
-  <si>
-    <t>LowSpeed</t>
-  </si>
-  <si>
-    <t>Kp</t>
-  </si>
-  <si>
-    <t>Kd</t>
-  </si>
-  <si>
-    <t>Ki</t>
-  </si>
-  <si>
-    <t>PID_Mult</t>
-  </si>
-  <si>
-    <t>PID_Konstante</t>
-  </si>
-  <si>
-    <t>LDR_Schwelle</t>
-  </si>
-  <si>
-    <t>Motor_Frequency</t>
-  </si>
-  <si>
-    <t>Interface_Frequency</t>
-  </si>
-  <si>
-    <t>US_Frequency</t>
-  </si>
-  <si>
-    <t>FocalLenght</t>
-  </si>
-  <si>
-    <t>ImageWidth</t>
-  </si>
-  <si>
-    <t>ImageHeight</t>
-  </si>
-  <si>
-    <t>ObjectSize</t>
-  </si>
-  <si>
-    <t>distFactor</t>
-  </si>
-  <si>
-    <t>Param</t>
-  </si>
-  <si>
-    <t>Line_Schwelle</t>
-  </si>
-  <si>
-    <t>Ir_Min[16]</t>
-  </si>
-  <si>
-    <t>Ir_Max[16]</t>
-  </si>
-  <si>
-    <t>0,0,0,0,0,…</t>
-  </si>
-  <si>
-    <t>3000,3000,…</t>
-  </si>
-  <si>
-    <t>VR_Motor</t>
-  </si>
-  <si>
-    <t>VL_Motor</t>
-  </si>
-  <si>
-    <t>HR_Motor</t>
-  </si>
-  <si>
-    <t>HL_Motor</t>
-  </si>
-  <si>
-    <t>VR_Speed_Port</t>
-  </si>
-  <si>
-    <t>VL_Speed_Port</t>
-  </si>
-  <si>
-    <t>HR_Speed_Port</t>
-  </si>
-  <si>
-    <t>HL_Speed_Port</t>
-  </si>
-  <si>
-    <t>VR_ExpanderA</t>
-  </si>
-  <si>
-    <t>VR_ExpanderB</t>
-  </si>
-  <si>
-    <t>VL_ExpanderB</t>
-  </si>
-  <si>
-    <t>VL_ExpanderA</t>
-  </si>
-  <si>
-    <t>HR_ExpanderA</t>
-  </si>
-  <si>
-    <t>HR_ExpanderB</t>
-  </si>
-  <si>
-    <t>HL_ExpanderA</t>
-  </si>
-  <si>
-    <t>HL_ExpanderB</t>
-  </si>
-  <si>
-    <t>enum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">( Diese Werte werden nicht im Programm verändert nur gelesen. Es sind Variablen auf die von überall zugegriffen werden kann. Sie können im Ordner Elementar unter Param oder enum verändert oder erweitert werden </t>
-  </si>
-  <si>
-    <t>US_Left</t>
-  </si>
-  <si>
-    <t>0x70</t>
-  </si>
-  <si>
-    <t>0x71</t>
-  </si>
-  <si>
-    <t>US_Right</t>
-  </si>
-  <si>
-    <t>LDR_Port</t>
-  </si>
-  <si>
-    <t>Start_Port</t>
-  </si>
-  <si>
-    <t>Schuss_Port</t>
-  </si>
-  <si>
-    <t>Kicker_Port</t>
-  </si>
-  <si>
-    <t>Output_Reg</t>
-  </si>
-  <si>
-    <t>Input_Reg</t>
-  </si>
-  <si>
-    <t>Config_Reg</t>
-  </si>
-  <si>
-    <t>Input_Mode</t>
-  </si>
-  <si>
-    <t>Output_Mode</t>
-  </si>
-  <si>
-    <t>All_Off</t>
-  </si>
-  <si>
-    <t>All_On</t>
-  </si>
-  <si>
-    <t>0x01</t>
-  </si>
-  <si>
-    <t>0x00</t>
-  </si>
-  <si>
-    <t>0x03</t>
-  </si>
-  <si>
-    <t>0xFF</t>
-  </si>
-  <si>
-    <t>I2C_ITF_Main</t>
-  </si>
-  <si>
-    <t>0x20</t>
-  </si>
-  <si>
-    <t>0x21</t>
-  </si>
-  <si>
-    <t>0x22</t>
-  </si>
-  <si>
-    <t>0x40</t>
-  </si>
-  <si>
-    <t>I2C_Motor</t>
-  </si>
-  <si>
-    <t>I2C_ITF_Ex</t>
-  </si>
-  <si>
-    <t>I2C_INA219</t>
-  </si>
-  <si>
-    <t>I2C_BUS</t>
-  </si>
-  <si>
-    <t>Wire1</t>
-  </si>
-  <si>
-    <t>I2C_SPEED</t>
-  </si>
-  <si>
-    <t>UART_Debug</t>
-  </si>
-  <si>
-    <t>UART_Pixy</t>
-  </si>
-  <si>
-    <t>UART_1</t>
-  </si>
-  <si>
-    <t>UART_2</t>
-  </si>
-  <si>
-    <t>Serial</t>
-  </si>
-  <si>
-    <t>Serial3</t>
-  </si>
-  <si>
-    <t>Serial6</t>
-  </si>
-  <si>
-    <t>Serial7</t>
-  </si>
-  <si>
-    <t>PID einfluss während fahrt bewegung</t>
-  </si>
-  <si>
-    <t>PID Speed</t>
-  </si>
-  <si>
-    <t>Ab welchem Lichtwert der LDR auslöst</t>
-  </si>
-  <si>
-    <t>Ab welchem Lichtwert der LinienSensor auslöst</t>
-  </si>
-  <si>
-    <t>Motor PWM Frquenz</t>
-  </si>
-  <si>
-    <t>Abfrage Frequenz der Buttons und Schalter ( =&gt; 100millis )</t>
-  </si>
-  <si>
-    <t>Abfrage Frequenz der US Sensoren ( =&gt; 100millis )</t>
-  </si>
-  <si>
-    <t>Kalibrationswerte für ir Sensoren falls es probleme gibt.</t>
-  </si>
-  <si>
-    <t>Motor Port an welchem der Motor VornRechts angeschlossen ist</t>
-  </si>
-  <si>
-    <t>Motor Port an welchem der Motor VornLinks angeschlossen ist</t>
-  </si>
-  <si>
-    <t>Motor Port an welchem der Motor HintenRechts angeschlossen ist</t>
-  </si>
-  <si>
-    <t>Motor Port an welchem der Motor HintenLinks angeschlossen ist</t>
-  </si>
-  <si>
-    <t>PWM Port</t>
-  </si>
-  <si>
-    <t>Richtungs Port  am Teensy</t>
-  </si>
-  <si>
-    <t>Addresse</t>
-  </si>
-  <si>
-    <t>Port am Teensy</t>
-  </si>
-  <si>
-    <t>register</t>
-  </si>
-  <si>
-    <t>I2C Port auf Basic Platine</t>
-  </si>
-  <si>
-    <t>Frequenz ( 1MHz )</t>
-  </si>
-  <si>
-    <t>Serieller Debug Port</t>
-  </si>
-  <si>
-    <t>Serieller Cam Port</t>
-  </si>
-  <si>
-    <t>Serieller Port 1</t>
-  </si>
-  <si>
-    <t>Serieller Port 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anmerkung: Diese Bezeichnung wird immer zum aufrufen aller Motor befehle verwendet um schnelle Logik mit bezug zur wirklich keit zu gewährleisten. </t>
-  </si>
-  <si>
-    <t>Motor befehl sieht dann so aus : Motor.On(VR_Motor,100);</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1692,22 +1692,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:I143"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="23.88671875" customWidth="1"/>
-    <col min="2" max="2" width="19.88671875" customWidth="1"/>
-    <col min="3" max="3" width="19.109375" customWidth="1"/>
-    <col min="4" max="4" width="112.21875" customWidth="1"/>
-    <col min="5" max="5" width="99.6640625" customWidth="1"/>
+    <col min="1" max="1" width="23.85546875" customWidth="1"/>
+    <col min="2" max="2" width="19.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.140625" customWidth="1"/>
+    <col min="4" max="4" width="112.28515625" customWidth="1"/>
+    <col min="5" max="5" width="99.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1724,7 +1727,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1739,7 +1742,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1748,1578 +1751,1578 @@
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s">
-        <v>103</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="C6" s="8"/>
       <c r="D6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>115</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E18" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B19" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D19" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B20" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B21" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B22" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C22" s="3"/>
       <c r="D22" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B23" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C23" s="3"/>
       <c r="D23" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B24" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C24" s="3"/>
       <c r="D24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B25" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C25" s="3"/>
       <c r="D25" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B26" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C26" s="3"/>
       <c r="D26" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B27" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B28" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B29" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>51</v>
-      </c>
       <c r="B30" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B31" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B32" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B33" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B34" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C34" s="3"/>
       <c r="D34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B35" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C35" s="3"/>
       <c r="D35" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="B36" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="B37" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="B38" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C38" s="10"/>
       <c r="D38" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="B39" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="B40" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C40" s="10"/>
       <c r="D40" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="B41" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="B42" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="C42" s="10"/>
       <c r="D42" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
       <c r="C43" s="2"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="B44" t="s">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="E44" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>123</v>
+        <v>86</v>
       </c>
       <c r="B45" t="s">
-        <v>124</v>
+        <v>87</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
       <c r="C46" s="2"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5">
       <c r="A47" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
       <c r="A48" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="B48" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
       <c r="A52" s="1" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="B52" s="7"/>
       <c r="C52" s="1"/>
       <c r="D52" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="B53" t="s">
-        <v>137</v>
+        <v>97</v>
       </c>
       <c r="C53" t="s">
-        <v>138</v>
+        <v>98</v>
       </c>
       <c r="D53" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>136</v>
+        <v>100</v>
       </c>
       <c r="B54" t="s">
-        <v>155</v>
+        <v>101</v>
       </c>
       <c r="C54">
         <v>50</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>140</v>
+        <v>102</v>
       </c>
       <c r="B55" t="s">
-        <v>155</v>
+        <v>101</v>
       </c>
       <c r="C55">
         <v>30</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>141</v>
+        <v>103</v>
       </c>
       <c r="B56" t="s">
-        <v>155</v>
+        <v>101</v>
       </c>
       <c r="C56" s="11">
         <v>46055</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>142</v>
+        <v>104</v>
       </c>
       <c r="B57" t="s">
-        <v>155</v>
+        <v>101</v>
       </c>
       <c r="C57">
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>143</v>
+        <v>105</v>
       </c>
       <c r="B58" t="s">
-        <v>155</v>
+        <v>101</v>
       </c>
       <c r="C58">
         <v>1.6000000000000001E-3</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>144</v>
+        <v>106</v>
       </c>
       <c r="B59" t="s">
-        <v>155</v>
+        <v>101</v>
       </c>
       <c r="C59">
         <v>0.1</v>
       </c>
       <c r="D59" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>145</v>
+        <v>108</v>
       </c>
       <c r="B60" t="s">
-        <v>155</v>
+        <v>101</v>
       </c>
       <c r="C60">
         <v>0.6</v>
       </c>
       <c r="D60" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>146</v>
+        <v>110</v>
       </c>
       <c r="B61" t="s">
-        <v>155</v>
+        <v>101</v>
       </c>
       <c r="C61">
         <v>500</v>
       </c>
       <c r="D61" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>156</v>
+        <v>112</v>
       </c>
       <c r="B62" t="s">
-        <v>155</v>
+        <v>101</v>
       </c>
       <c r="C62">
         <v>2900</v>
       </c>
       <c r="D62" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
       <c r="A63" t="s">
-        <v>147</v>
+        <v>114</v>
       </c>
       <c r="B63" t="s">
-        <v>155</v>
+        <v>101</v>
       </c>
       <c r="C63">
         <v>400</v>
       </c>
       <c r="D63" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
       <c r="A64" t="s">
-        <v>148</v>
+        <v>116</v>
       </c>
       <c r="B64" t="s">
-        <v>155</v>
+        <v>101</v>
       </c>
       <c r="C64">
         <v>10</v>
       </c>
       <c r="D64" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
       <c r="A65" t="s">
-        <v>149</v>
+        <v>118</v>
       </c>
       <c r="B65" t="s">
-        <v>155</v>
+        <v>101</v>
       </c>
       <c r="C65">
         <v>10</v>
       </c>
       <c r="D65" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
       <c r="A66" t="s">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="B66" t="s">
-        <v>155</v>
+        <v>101</v>
       </c>
       <c r="C66">
         <v>2040</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9">
       <c r="A67" t="s">
-        <v>151</v>
+        <v>121</v>
       </c>
       <c r="B67" t="s">
-        <v>155</v>
+        <v>101</v>
       </c>
       <c r="C67">
         <v>2952</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9">
       <c r="A68" t="s">
-        <v>152</v>
+        <v>122</v>
       </c>
       <c r="B68" t="s">
-        <v>155</v>
+        <v>101</v>
       </c>
       <c r="C68">
         <v>1944</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9">
       <c r="A69" t="s">
-        <v>153</v>
+        <v>123</v>
       </c>
       <c r="B69" t="s">
-        <v>155</v>
+        <v>101</v>
       </c>
       <c r="C69">
         <v>4.2670000000000003</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9">
       <c r="A70" t="s">
-        <v>154</v>
+        <v>124</v>
       </c>
       <c r="B70" t="s">
-        <v>155</v>
+        <v>101</v>
       </c>
       <c r="C70">
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9">
       <c r="A71" t="s">
-        <v>157</v>
+        <v>125</v>
       </c>
       <c r="B71" t="s">
-        <v>155</v>
+        <v>101</v>
       </c>
       <c r="C71" t="s">
-        <v>159</v>
+        <v>126</v>
       </c>
       <c r="D71" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9">
       <c r="A72" t="s">
-        <v>158</v>
+        <v>128</v>
       </c>
       <c r="B72" t="s">
-        <v>155</v>
+        <v>101</v>
       </c>
       <c r="C72" t="s">
-        <v>160</v>
+        <v>129</v>
       </c>
       <c r="D72" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9">
       <c r="A74" t="s">
-        <v>161</v>
+        <v>130</v>
       </c>
       <c r="B74" t="s">
-        <v>177</v>
+        <v>131</v>
       </c>
       <c r="C74">
         <v>4</v>
       </c>
       <c r="D74" t="s">
-        <v>225</v>
+        <v>132</v>
       </c>
       <c r="E74" s="12" t="s">
-        <v>240</v>
+        <v>133</v>
       </c>
       <c r="F74" s="13"/>
       <c r="G74" s="13"/>
       <c r="H74" s="13"/>
       <c r="I74" s="13"/>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9">
       <c r="A75" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="B75" t="s">
-        <v>177</v>
+        <v>131</v>
       </c>
       <c r="C75">
         <v>3</v>
       </c>
       <c r="D75" t="s">
-        <v>226</v>
+        <v>135</v>
       </c>
       <c r="E75" s="12" t="s">
-        <v>241</v>
+        <v>136</v>
       </c>
       <c r="F75" s="13"/>
       <c r="G75" s="13"/>
       <c r="H75" s="13"/>
       <c r="I75" s="13"/>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9">
       <c r="A76" t="s">
-        <v>163</v>
+        <v>137</v>
       </c>
       <c r="B76" t="s">
-        <v>177</v>
+        <v>131</v>
       </c>
       <c r="C76">
         <v>1</v>
       </c>
       <c r="D76" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9">
       <c r="A77" t="s">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="B77" t="s">
-        <v>177</v>
+        <v>131</v>
       </c>
       <c r="C77">
         <v>2</v>
       </c>
       <c r="D77" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9">
       <c r="A79" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="B79" t="s">
-        <v>177</v>
+        <v>131</v>
       </c>
       <c r="C79">
         <v>9</v>
       </c>
       <c r="D79" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9">
       <c r="A80" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="B80" t="s">
-        <v>177</v>
+        <v>131</v>
       </c>
       <c r="C80">
         <v>6</v>
       </c>
       <c r="D80" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
       <c r="B81" t="s">
-        <v>177</v>
+        <v>131</v>
       </c>
       <c r="C81">
         <v>4</v>
       </c>
       <c r="D81" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="B82" t="s">
-        <v>177</v>
+        <v>131</v>
       </c>
       <c r="C82">
         <v>5</v>
       </c>
       <c r="D82" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="B84" t="s">
-        <v>177</v>
+        <v>131</v>
       </c>
       <c r="C84">
         <v>26</v>
       </c>
       <c r="D84" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>170</v>
+        <v>148</v>
       </c>
       <c r="B85" t="s">
-        <v>177</v>
+        <v>131</v>
       </c>
       <c r="C85">
         <v>32</v>
       </c>
       <c r="D85" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="B86" t="s">
-        <v>177</v>
+        <v>131</v>
       </c>
       <c r="C86">
         <v>8</v>
       </c>
       <c r="D86" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>171</v>
+        <v>150</v>
       </c>
       <c r="B87" t="s">
-        <v>177</v>
+        <v>131</v>
       </c>
       <c r="C87">
         <v>7</v>
       </c>
       <c r="D87" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="B88" t="s">
-        <v>177</v>
+        <v>131</v>
       </c>
       <c r="C88">
         <v>0</v>
       </c>
       <c r="D88" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
       <c r="B89" t="s">
-        <v>177</v>
+        <v>131</v>
       </c>
       <c r="C89">
         <v>1</v>
       </c>
       <c r="D89" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="B90" t="s">
-        <v>177</v>
+        <v>131</v>
       </c>
       <c r="C90">
         <v>2</v>
       </c>
       <c r="D90" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="B91" t="s">
-        <v>177</v>
+        <v>131</v>
       </c>
       <c r="C91">
         <v>3</v>
       </c>
       <c r="D91" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>179</v>
+        <v>155</v>
       </c>
       <c r="B93" t="s">
-        <v>177</v>
+        <v>131</v>
       </c>
       <c r="C93" t="s">
-        <v>180</v>
+        <v>156</v>
       </c>
       <c r="D93" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>182</v>
+        <v>158</v>
       </c>
       <c r="B94" t="s">
-        <v>177</v>
+        <v>131</v>
       </c>
       <c r="C94" t="s">
-        <v>181</v>
+        <v>159</v>
       </c>
       <c r="D94" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
       <c r="A96" t="s">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="B96" t="s">
-        <v>177</v>
+        <v>131</v>
       </c>
       <c r="C96">
         <v>23</v>
       </c>
       <c r="D96" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
       <c r="A97" t="s">
-        <v>184</v>
+        <v>162</v>
       </c>
       <c r="B97" t="s">
-        <v>177</v>
+        <v>131</v>
       </c>
       <c r="C97">
         <v>10</v>
       </c>
       <c r="D97" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
       <c r="A98" t="s">
-        <v>185</v>
+        <v>163</v>
       </c>
       <c r="B98" t="s">
-        <v>177</v>
+        <v>131</v>
       </c>
       <c r="C98">
         <v>30</v>
       </c>
       <c r="D98" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
       <c r="A99" t="s">
-        <v>186</v>
+        <v>164</v>
       </c>
       <c r="B99" t="s">
-        <v>177</v>
+        <v>131</v>
       </c>
       <c r="C99">
         <v>3</v>
       </c>
       <c r="D99" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
       <c r="A101" t="s">
+        <v>165</v>
+      </c>
+      <c r="B101" t="s">
+        <v>131</v>
+      </c>
+      <c r="C101" t="s">
+        <v>166</v>
+      </c>
+      <c r="D101" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102" t="s">
+        <v>168</v>
+      </c>
+      <c r="B102" t="s">
+        <v>131</v>
+      </c>
+      <c r="C102" t="s">
+        <v>169</v>
+      </c>
+      <c r="D102" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
+      <c r="A103" t="s">
+        <v>170</v>
+      </c>
+      <c r="B103" t="s">
+        <v>131</v>
+      </c>
+      <c r="C103" t="s">
+        <v>171</v>
+      </c>
+      <c r="D103" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104" t="s">
+        <v>172</v>
+      </c>
+      <c r="B104" t="s">
+        <v>131</v>
+      </c>
+      <c r="C104" t="s">
+        <v>173</v>
+      </c>
+      <c r="D104" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105" t="s">
+        <v>174</v>
+      </c>
+      <c r="B105" t="s">
+        <v>131</v>
+      </c>
+      <c r="C105" t="s">
+        <v>169</v>
+      </c>
+      <c r="D105" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" t="s">
+        <v>175</v>
+      </c>
+      <c r="B106" t="s">
+        <v>131</v>
+      </c>
+      <c r="C106" t="s">
+        <v>169</v>
+      </c>
+      <c r="D106" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" t="s">
+        <v>176</v>
+      </c>
+      <c r="B107" t="s">
+        <v>131</v>
+      </c>
+      <c r="C107" t="s">
+        <v>173</v>
+      </c>
+      <c r="D107" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109" t="s">
+        <v>177</v>
+      </c>
+      <c r="B109" t="s">
+        <v>131</v>
+      </c>
+      <c r="C109" t="s">
+        <v>178</v>
+      </c>
+      <c r="D109" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4">
+      <c r="A110" t="s">
+        <v>179</v>
+      </c>
+      <c r="B110" t="s">
+        <v>131</v>
+      </c>
+      <c r="C110" t="s">
+        <v>180</v>
+      </c>
+      <c r="D110" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" t="s">
+        <v>181</v>
+      </c>
+      <c r="B111" t="s">
+        <v>131</v>
+      </c>
+      <c r="C111" t="s">
+        <v>182</v>
+      </c>
+      <c r="D111" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" t="s">
+        <v>183</v>
+      </c>
+      <c r="B112" t="s">
+        <v>131</v>
+      </c>
+      <c r="C112" t="s">
+        <v>184</v>
+      </c>
+      <c r="D112" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4">
+      <c r="A114" t="s">
+        <v>185</v>
+      </c>
+      <c r="B114" t="s">
+        <v>131</v>
+      </c>
+      <c r="C114" t="s">
+        <v>186</v>
+      </c>
+      <c r="D114" t="s">
         <v>187</v>
       </c>
-      <c r="B101" t="s">
-        <v>177</v>
-      </c>
-      <c r="C101" t="s">
-        <v>194</v>
-      </c>
-      <c r="D101" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
+    </row>
+    <row r="115" spans="1:4">
+      <c r="A115" t="s">
         <v>188</v>
       </c>
-      <c r="B102" t="s">
-        <v>177</v>
-      </c>
-      <c r="C102" t="s">
-        <v>195</v>
-      </c>
-      <c r="D102" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
-        <v>189</v>
-      </c>
-      <c r="B103" t="s">
-        <v>177</v>
-      </c>
-      <c r="C103" t="s">
-        <v>196</v>
-      </c>
-      <c r="D103" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
-        <v>190</v>
-      </c>
-      <c r="B104" t="s">
-        <v>177</v>
-      </c>
-      <c r="C104" t="s">
-        <v>197</v>
-      </c>
-      <c r="D104" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A105" t="s">
-        <v>191</v>
-      </c>
-      <c r="B105" t="s">
-        <v>177</v>
-      </c>
-      <c r="C105" t="s">
-        <v>195</v>
-      </c>
-      <c r="D105" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A106" t="s">
-        <v>192</v>
-      </c>
-      <c r="B106" t="s">
-        <v>177</v>
-      </c>
-      <c r="C106" t="s">
-        <v>195</v>
-      </c>
-      <c r="D106" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A107" t="s">
-        <v>193</v>
-      </c>
-      <c r="B107" t="s">
-        <v>177</v>
-      </c>
-      <c r="C107" t="s">
-        <v>197</v>
-      </c>
-      <c r="D107" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A109" t="s">
-        <v>198</v>
-      </c>
-      <c r="B109" t="s">
-        <v>177</v>
-      </c>
-      <c r="C109" t="s">
-        <v>199</v>
-      </c>
-      <c r="D109" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A110" t="s">
-        <v>203</v>
-      </c>
-      <c r="B110" t="s">
-        <v>177</v>
-      </c>
-      <c r="C110" t="s">
-        <v>200</v>
-      </c>
-      <c r="D110" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A111" t="s">
-        <v>204</v>
-      </c>
-      <c r="B111" t="s">
-        <v>177</v>
-      </c>
-      <c r="C111" t="s">
-        <v>201</v>
-      </c>
-      <c r="D111" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A112" t="s">
-        <v>205</v>
-      </c>
-      <c r="B112" t="s">
-        <v>177</v>
-      </c>
-      <c r="C112" t="s">
-        <v>202</v>
-      </c>
-      <c r="D112" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A114" t="s">
-        <v>206</v>
-      </c>
-      <c r="B114" t="s">
-        <v>177</v>
-      </c>
-      <c r="C114" t="s">
-        <v>207</v>
-      </c>
-      <c r="D114" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A115" t="s">
-        <v>208</v>
-      </c>
       <c r="B115" t="s">
-        <v>177</v>
+        <v>131</v>
       </c>
       <c r="C115">
         <v>1000000</v>
       </c>
       <c r="D115" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4">
       <c r="A117" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="B117" t="s">
-        <v>177</v>
+        <v>131</v>
       </c>
       <c r="C117" t="s">
-        <v>213</v>
+        <v>191</v>
       </c>
       <c r="D117" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4">
       <c r="A118" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="B118" t="s">
-        <v>177</v>
+        <v>131</v>
       </c>
       <c r="C118" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="D118" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4">
       <c r="A119" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="B119" t="s">
-        <v>177</v>
+        <v>131</v>
       </c>
       <c r="C119" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
       <c r="D119" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4">
       <c r="A120" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="B120" t="s">
-        <v>177</v>
+        <v>131</v>
       </c>
       <c r="C120" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="D120" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4">
       <c r="A127" s="1" t="s">
-        <v>71</v>
+        <v>202</v>
       </c>
       <c r="B127" s="1"/>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:4">
       <c r="A128" t="s">
         <v>1</v>
       </c>
       <c r="B128" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="C128" t="s">
-        <v>73</v>
+        <v>203</v>
       </c>
       <c r="D128" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:4">
       <c r="A129" t="s">
-        <v>115</v>
+        <v>21</v>
       </c>
       <c r="B129" t="s">
-        <v>74</v>
+        <v>204</v>
       </c>
       <c r="C129" t="s">
-        <v>75</v>
+        <v>205</v>
       </c>
       <c r="D129" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4">
       <c r="A130" t="s">
-        <v>115</v>
+        <v>21</v>
       </c>
       <c r="B130" t="s">
-        <v>77</v>
+        <v>207</v>
       </c>
       <c r="C130" t="s">
-        <v>78</v>
+        <v>208</v>
       </c>
       <c r="D130" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4">
       <c r="A131" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B131" t="s">
-        <v>80</v>
+        <v>210</v>
       </c>
       <c r="C131" t="s">
-        <v>81</v>
+        <v>211</v>
       </c>
       <c r="D131" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4">
+      <c r="A132" t="s">
+        <v>43</v>
+      </c>
+      <c r="B132" t="s">
+        <v>213</v>
+      </c>
+      <c r="C132" t="s">
+        <v>214</v>
+      </c>
+      <c r="D132" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4">
+      <c r="A133" t="s">
+        <v>43</v>
+      </c>
+      <c r="B133" t="s">
+        <v>216</v>
+      </c>
+      <c r="C133" t="s">
+        <v>211</v>
+      </c>
+      <c r="D133" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4">
+      <c r="A134" t="s">
+        <v>43</v>
+      </c>
+      <c r="B134" t="s">
+        <v>218</v>
+      </c>
+      <c r="C134" t="s">
+        <v>211</v>
+      </c>
+      <c r="D134" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4">
+      <c r="A135" t="s">
+        <v>70</v>
+      </c>
+      <c r="B135" t="s">
+        <v>220</v>
+      </c>
+      <c r="C135" t="s">
+        <v>211</v>
+      </c>
+      <c r="D135" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4">
+      <c r="A136" t="s">
+        <v>70</v>
+      </c>
+      <c r="B136" t="s">
+        <v>222</v>
+      </c>
+      <c r="C136" t="s">
+        <v>211</v>
+      </c>
+      <c r="D136" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4">
+      <c r="A137" t="s">
+        <v>70</v>
+      </c>
+      <c r="B137" t="s">
+        <v>224</v>
+      </c>
+      <c r="C137" t="s">
+        <v>225</v>
+      </c>
+      <c r="D137" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4">
+      <c r="A138" t="s">
+        <v>70</v>
+      </c>
+      <c r="B138" t="s">
+        <v>227</v>
+      </c>
+      <c r="C138" t="s">
+        <v>228</v>
+      </c>
+      <c r="D138" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4">
+      <c r="A139" t="s">
+        <v>21</v>
+      </c>
+      <c r="B139" t="s">
+        <v>230</v>
+      </c>
+      <c r="C139" t="s">
+        <v>231</v>
+      </c>
+      <c r="D139" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4">
+      <c r="A140" t="s">
+        <v>86</v>
+      </c>
+      <c r="B140" t="s">
+        <v>233</v>
+      </c>
+      <c r="C140" t="s">
+        <v>234</v>
+      </c>
+      <c r="D140" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4">
+      <c r="A141" t="s">
+        <v>86</v>
+      </c>
+      <c r="B141" t="s">
+        <v>236</v>
+      </c>
+      <c r="C141" t="s">
+        <v>234</v>
+      </c>
+      <c r="D141" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4">
+      <c r="A142" t="s">
+        <v>86</v>
+      </c>
+      <c r="B142" t="s">
+        <v>216</v>
+      </c>
+      <c r="C142" t="s">
+        <v>238</v>
+      </c>
+      <c r="D142" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4">
+      <c r="A143" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A132" t="s">
-        <v>39</v>
-      </c>
-      <c r="B132" t="s">
-        <v>83</v>
-      </c>
-      <c r="C132" t="s">
-        <v>84</v>
-      </c>
-      <c r="D132" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A133" t="s">
-        <v>39</v>
-      </c>
-      <c r="B133" t="s">
-        <v>86</v>
-      </c>
-      <c r="C133" t="s">
-        <v>81</v>
-      </c>
-      <c r="D133" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A134" t="s">
-        <v>39</v>
-      </c>
-      <c r="B134" t="s">
-        <v>88</v>
-      </c>
-      <c r="C134" t="s">
-        <v>81</v>
-      </c>
-      <c r="D134" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A135" t="s">
-        <v>90</v>
-      </c>
-      <c r="B135" t="s">
-        <v>105</v>
-      </c>
-      <c r="C135" t="s">
-        <v>81</v>
-      </c>
-      <c r="D135" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A136" t="s">
-        <v>90</v>
-      </c>
-      <c r="B136" t="s">
-        <v>108</v>
-      </c>
-      <c r="C136" t="s">
-        <v>81</v>
-      </c>
-      <c r="D136" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A137" t="s">
-        <v>90</v>
-      </c>
-      <c r="B137" t="s">
-        <v>109</v>
-      </c>
-      <c r="C137" t="s">
-        <v>111</v>
-      </c>
-      <c r="D137" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A138" t="s">
-        <v>90</v>
-      </c>
-      <c r="B138" t="s">
-        <v>110</v>
-      </c>
-      <c r="C138" t="s">
-        <v>112</v>
-      </c>
-      <c r="D138" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A139" t="s">
-        <v>115</v>
-      </c>
-      <c r="B139" t="s">
-        <v>116</v>
-      </c>
-      <c r="C139" t="s">
-        <v>117</v>
-      </c>
-      <c r="D139" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A140" t="s">
-        <v>123</v>
-      </c>
-      <c r="B140" t="s">
-        <v>126</v>
-      </c>
-      <c r="C140" t="s">
-        <v>127</v>
-      </c>
-      <c r="D140" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A141" t="s">
-        <v>123</v>
-      </c>
-      <c r="B141" t="s">
-        <v>129</v>
-      </c>
-      <c r="C141" t="s">
-        <v>127</v>
-      </c>
-      <c r="D141" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A142" t="s">
-        <v>123</v>
-      </c>
-      <c r="B142" t="s">
-        <v>86</v>
-      </c>
-      <c r="C142" t="s">
-        <v>131</v>
-      </c>
-      <c r="D142" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A143" t="s">
-        <v>119</v>
-      </c>
       <c r="B143" t="s">
-        <v>133</v>
+        <v>240</v>
       </c>
       <c r="C143" t="s">
-        <v>127</v>
+        <v>234</v>
       </c>
       <c r="D143" t="s">
-        <v>134</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>
